--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -27842,7 +27842,7 @@
         <v>34000</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.238000005483627</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="D1195" t="n">
         <v>0.219999998807907</v>
@@ -27854,6 +27854,29 @@
         <v>0.247999995946884</v>
       </c>
       <c r="G1195" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1196" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G1196" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -27880,6 +27880,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>77000</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1197" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -27903,6 +27903,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1198" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>0.224000006914139</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="G1198" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -27926,6 +27926,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>83000</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="G1199" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -27767,22 +27767,22 @@
     </row>
     <row r="1192">
       <c r="A1192" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1192" t="n">
-        <v>54000</v>
+        <v>11000</v>
       </c>
       <c r="C1192" t="n">
-        <v>0.241999998688698</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="D1192" t="n">
-        <v>0.228000000119209</v>
+        <v>0.236000001430511</v>
       </c>
       <c r="E1192" t="n">
-        <v>0.241999998688698</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="F1192" t="n">
-        <v>0.230000004172325</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="G1192" t="s">
         <v>7</v>
@@ -27790,22 +27790,22 @@
     </row>
     <row r="1193">
       <c r="A1193" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1193" t="n">
-        <v>32000</v>
+        <v>54000</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.236000001430511</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1193" t="n">
-        <v>0.224000006914139</v>
+        <v>0.228000000119209</v>
       </c>
       <c r="E1193" t="n">
-        <v>0.23199999332428</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1193" t="n">
-        <v>0.228000000119209</v>
+        <v>0.230000004172325</v>
       </c>
       <c r="G1193" t="s">
         <v>7</v>
@@ -27813,22 +27813,22 @@
     </row>
     <row r="1194">
       <c r="A1194" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1194" t="n">
-        <v>78000</v>
+        <v>32000</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.244000002741814</v>
+        <v>0.236000001430511</v>
       </c>
       <c r="D1194" t="n">
-        <v>0.222000002861023</v>
+        <v>0.224000006914139</v>
       </c>
       <c r="E1194" t="n">
-        <v>0.222000002861023</v>
+        <v>0.23199999332428</v>
       </c>
       <c r="F1194" t="n">
-        <v>0.230000004172325</v>
+        <v>0.228000000119209</v>
       </c>
       <c r="G1194" t="s">
         <v>7</v>
@@ -27836,22 +27836,22 @@
     </row>
     <row r="1195">
       <c r="A1195" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1195" t="n">
-        <v>34000</v>
+        <v>78000</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.247999995946884</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1195" t="n">
-        <v>0.219999998807907</v>
+        <v>0.222000002861023</v>
       </c>
       <c r="E1195" t="n">
-        <v>0.224000006914139</v>
+        <v>0.222000002861023</v>
       </c>
       <c r="F1195" t="n">
-        <v>0.247999995946884</v>
+        <v>0.230000004172325</v>
       </c>
       <c r="G1195" t="s">
         <v>7</v>
@@ -27859,22 +27859,22 @@
     </row>
     <row r="1196">
       <c r="A1196" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1196" t="n">
-        <v>32000</v>
+        <v>34000</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.25</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="D1196" t="n">
-        <v>0.23199999332428</v>
+        <v>0.219999998807907</v>
       </c>
       <c r="E1196" t="n">
-        <v>0.25</v>
+        <v>0.224000006914139</v>
       </c>
       <c r="F1196" t="n">
-        <v>0.238000005483627</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="G1196" t="s">
         <v>7</v>
@@ -27882,22 +27882,22 @@
     </row>
     <row r="1197">
       <c r="A1197" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1197" t="n">
-        <v>77000</v>
+        <v>32000</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.261999994516373</v>
+        <v>0.25</v>
       </c>
       <c r="D1197" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1197" t="n">
         <v>0.238000005483627</v>
-      </c>
-      <c r="E1197" t="n">
-        <v>0.239999994635582</v>
-      </c>
-      <c r="F1197" t="n">
-        <v>0.241999998688698</v>
       </c>
       <c r="G1197" t="s">
         <v>7</v>
@@ -27905,22 +27905,22 @@
     </row>
     <row r="1198">
       <c r="A1198" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1198" t="n">
-        <v>9000</v>
+        <v>77000</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.244000002741814</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="D1198" t="n">
-        <v>0.224000006914139</v>
+        <v>0.238000005483627</v>
       </c>
       <c r="E1198" t="n">
-        <v>0.244000002741814</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1198" t="n">
-        <v>0.228000000119209</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1198" t="s">
         <v>7</v>
@@ -27928,24 +27928,47 @@
     </row>
     <row r="1199">
       <c r="A1199" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1199" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>0.224000006914139</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="G1199" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1200" t="n">
         <v>83000</v>
       </c>
-      <c r="C1199" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D1199" t="n">
+      <c r="C1200" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="F1200" t="n">
         <v>0.222000002861023</v>
       </c>
-      <c r="E1199" t="n">
-        <v>0.230000004172325</v>
-      </c>
-      <c r="F1199" t="n">
-        <v>0.23199999332428</v>
-      </c>
-      <c r="G1199" t="s">
+      <c r="G1200" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -31627,6 +31627,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>43000</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>0.209999993443489</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="H1203" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -31653,6 +31653,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>53000</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="H1204" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -31679,6 +31679,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="H1205" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -31687,7 +31687,7 @@
         <v>30000</v>
       </c>
       <c r="C1205" t="n">
-        <v>0.270000010728836</v>
+        <v>0.280000001192093</v>
       </c>
       <c r="D1205" t="n">
         <v>0.25</v>
@@ -31702,6 +31702,32 @@
         <v>0.280000001192093</v>
       </c>
       <c r="H1205" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>69000</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="H1206" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -31783,6 +31783,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>129000</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>0.293999999761581</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -28241,8 +28241,31 @@
       <c r="E1212" t="n">
         <v>0.263999998569489</v>
       </c>
-      <c r="F1212"/>
+      <c r="F1212" t="n">
+        <v>0.254000008106232</v>
+      </c>
       <c r="G1212" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="F1213"/>
+      <c r="G1213" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -28259,13 +28259,36 @@
         <v>0.261999994516373</v>
       </c>
       <c r="D1213" t="n">
-        <v>0.25</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1213" t="n">
         <v>0.254000008106232</v>
       </c>
-      <c r="F1213"/>
+      <c r="F1213" t="n">
+        <v>0.241999998688698</v>
+      </c>
       <c r="G1213" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1214" t="n">
+        <v>39000</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1214"/>
+      <c r="G1214" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -28287,8 +28287,31 @@
       <c r="E1214" t="n">
         <v>0.241999998688698</v>
       </c>
-      <c r="F1214"/>
+      <c r="F1214" t="n">
+        <v>0.225999996066093</v>
+      </c>
       <c r="G1214" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>116000</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>0.236000001430511</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>0.206000000238419</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="F1215"/>
+      <c r="G1215" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -28310,8 +28310,31 @@
       <c r="E1215" t="n">
         <v>0.225999996066093</v>
       </c>
-      <c r="F1215"/>
+      <c r="F1215" t="n">
+        <v>0.228000000119209</v>
+      </c>
       <c r="G1215" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1216" t="n">
+        <v>86000</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>0.236000001430511</v>
+      </c>
+      <c r="F1216"/>
+      <c r="G1216" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -28340,6 +28340,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>0.217999994754791</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="G1217" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -32069,6 +32069,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="H1220" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -32095,6 +32095,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>113000</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>0.275999993085861</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>0.272000014781952</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="H1221" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -35787,6 +35787,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1222">
+      <c r="A1222" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1222" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="H1222" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1223" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1223" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -35845,6 +35845,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1224">
+      <c r="A1224" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1224" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="H1224" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -35874,6 +35874,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1225">
+      <c r="A1225" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1225" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="H1225" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1225" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -35903,6 +35903,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1226" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="H1226" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -35932,6 +35932,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1227" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>0.263999998569489</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -35961,6 +35961,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1228" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>26000</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -35990,6 +35990,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1229" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>42000</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -36019,6 +36019,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1230" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="H1230" t="n">
+        <v>48000</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTC.MI.xlsx
+++ b/data/FTC.MI.xlsx
@@ -36048,6 +36048,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1231">
+      <c r="A1231" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1231" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
